--- a/data/All_Projects.xlsx
+++ b/data/All_Projects.xlsx
@@ -504,7 +504,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="E10" s="25" t="n">
-        <x:v>0</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="F10" s="18" t="s">
         <x:v>31</x:v>

--- a/data/All_Projects.xlsx
+++ b/data/All_Projects.xlsx
@@ -504,7 +504,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="E10" s="25" t="n">
-        <x:v>300000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F10" s="18" t="s">
         <x:v>31</x:v>

--- a/data/All_Projects.xlsx
+++ b/data/All_Projects.xlsx
@@ -149,6 +149,15 @@
   </x:si>
   <x:si>
     <x:t>Media: Innovation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-UCMC-079</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UChicago Service Lines - Media Management</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEW / IN ESTIMATING</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -306,7 +315,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:dimension ref="A1:G17"/>
+  <x:dimension ref="A1:G18"/>
   <x:sheetFormatPr defaultRowHeight="12.75"/>
   <x:cols>
     <x:col min="1" max="1" width="13.711" customWidth="1"/>
@@ -504,7 +513,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="E10" s="25" t="n">
-        <x:v>0</x:v>
+        <x:v>181930.6</x:v>
       </x:c>
       <x:c r="F10" s="18" t="s">
         <x:v>31</x:v>
@@ -610,14 +619,34 @@
         <x:v>45</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="13.4" customHeight="1"/>
-    <x:row r="17" ht="12" customHeight="1">
-      <x:c r="A17" s="31"/>
-      <x:c r="B17" s="31"/>
-      <x:c r="C17" s="31"/>
-      <x:c r="D17" s="31"/>
-      <x:c r="E17" s="31"/>
-      <x:c r="F17" s="31"/>
+    <x:row r="16" ht="13.05" customHeight="1">
+      <x:c r="A16" s="18" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B16" s="18" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C16" s="18" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D16" s="18" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E16" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F16" s="18" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="13.4" customHeight="1"/>
+    <x:row r="18" ht="12" customHeight="1">
+      <x:c r="A18" s="31"/>
+      <x:c r="B18" s="31"/>
+      <x:c r="C18" s="31"/>
+      <x:c r="D18" s="31"/>
+      <x:c r="E18" s="31"/>
+      <x:c r="F18" s="31"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>

--- a/data/All_Projects.xlsx
+++ b/data/All_Projects.xlsx
@@ -149,15 +149,6 @@
   </x:si>
   <x:si>
     <x:t>Media: Innovation</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-UCMC-079</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UChicago Service Lines - Media Management</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NEW / IN ESTIMATING</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -315,7 +306,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:dimension ref="A1:G18"/>
+  <x:dimension ref="A1:G17"/>
   <x:sheetFormatPr defaultRowHeight="12.75"/>
   <x:cols>
     <x:col min="1" max="1" width="13.711" customWidth="1"/>
@@ -613,40 +604,20 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="E15" s="25" t="n">
-        <x:v>35000</x:v>
+        <x:v>115000</x:v>
       </x:c>
       <x:c r="F15" s="18" t="s">
         <x:v>45</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="13.05" customHeight="1">
-      <x:c r="A16" s="18" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B16" s="18" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C16" s="18" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D16" s="18" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E16" s="25" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F16" s="18" t="s">
-        <x:v>42</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="13.4" customHeight="1"/>
-    <x:row r="18" ht="12" customHeight="1">
-      <x:c r="A18" s="31"/>
-      <x:c r="B18" s="31"/>
-      <x:c r="C18" s="31"/>
-      <x:c r="D18" s="31"/>
-      <x:c r="E18" s="31"/>
-      <x:c r="F18" s="31"/>
+    <x:row r="16" ht="13.4" customHeight="1"/>
+    <x:row r="17" ht="12" customHeight="1">
+      <x:c r="A17" s="31"/>
+      <x:c r="B17" s="31"/>
+      <x:c r="C17" s="31"/>
+      <x:c r="D17" s="31"/>
+      <x:c r="E17" s="31"/>
+      <x:c r="F17" s="31"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>

--- a/data/All_Projects.xlsx
+++ b/data/All_Projects.xlsx
@@ -46,7 +46,7 @@
     <x:t>COMPLETE/EXPENSES PENDING</x:t>
   </x:si>
   <x:si>
-    <x:t>Creative: Concepting</x:t>
+    <x:t>Media: Labor</x:t>
   </x:si>
   <x:si>
     <x:t>26-UCMC-052</x:t>
@@ -137,9 +137,6 @@
   </x:si>
   <x:si>
     <x:t>UChicago Service Lines - Digestive Diseases and Transplant - Media Labor</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Media: Labor</x:t>
   </x:si>
   <x:si>
     <x:t>26-UCMC-072</x:t>
@@ -587,7 +584,7 @@
         <x:v>34000</x:v>
       </x:c>
       <x:c r="F14" s="18" t="s">
-        <x:v>42</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="13.05" customHeight="1">
@@ -595,10 +592,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B15" s="18" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C15" s="18" t="s">
         <x:v>43</x:v>
-      </x:c>
-      <x:c r="C15" s="18" t="s">
-        <x:v>44</x:v>
       </x:c>
       <x:c r="D15" s="18" t="s">
         <x:v>14</x:v>
@@ -607,7 +604,7 @@
         <x:v>115000</x:v>
       </x:c>
       <x:c r="F15" s="18" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="13.4" customHeight="1"/>

--- a/data/All_Projects.xlsx
+++ b/data/All_Projects.xlsx
@@ -501,7 +501,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="E10" s="25" t="n">
-        <x:v>181930.6</x:v>
+        <x:v>187030.6</x:v>
       </x:c>
       <x:c r="F10" s="18" t="s">
         <x:v>31</x:v>
